--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="304">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -315,7 +315,7 @@
     <t>86</t>
   </si>
   <si>
-    <t xml:space="preserve">Vaccination </t>
+    <t>Vaccination</t>
   </si>
   <si>
     <t>87</t>
@@ -1269,7 +1269,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -1281,7 +1283,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -1293,7 +1297,9 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -1305,7 +1311,9 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -1317,7 +1325,9 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -1329,7 +1339,9 @@
       <c r="C7" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -1341,7 +1353,9 @@
       <c r="C8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -1353,7 +1367,9 @@
       <c r="C9" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -1365,7 +1381,9 @@
       <c r="C10" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -1377,7 +1395,9 @@
       <c r="C11" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>62</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -1389,7 +1409,9 @@
       <c r="C12" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>64</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -1401,7 +1423,9 @@
       <c r="C13" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>66</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -1413,7 +1437,9 @@
       <c r="C14" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>68</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -1425,7 +1451,9 @@
       <c r="C15" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>70</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -1437,7 +1465,9 @@
       <c r="C16" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>72</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -1449,7 +1479,9 @@
       <c r="C17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>74</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -1461,7 +1493,9 @@
       <c r="C18" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
@@ -1473,7 +1507,9 @@
       <c r="C19" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
@@ -1485,7 +1521,9 @@
       <c r="C20" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>80</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
@@ -1497,7 +1535,9 @@
       <c r="C21" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>82</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
@@ -1509,7 +1549,9 @@
       <c r="C22" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>84</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
@@ -1521,7 +1563,9 @@
       <c r="C23" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="D23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>86</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
@@ -1533,7 +1577,9 @@
       <c r="C24" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="D24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>88</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
@@ -1545,7 +1591,9 @@
       <c r="C25" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="D25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>90</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
@@ -1557,7 +1605,9 @@
       <c r="C26" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="D26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>92</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
@@ -1569,7 +1619,9 @@
       <c r="C27" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="D27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>94</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
@@ -1581,7 +1633,9 @@
       <c r="C28" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="D28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>96</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
@@ -1593,7 +1647,9 @@
       <c r="C29" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="D29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>98</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
@@ -1605,7 +1661,9 @@
       <c r="C30" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="D30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>100</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
@@ -1617,7 +1675,9 @@
       <c r="C31" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="D31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>102</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
@@ -1629,7 +1689,9 @@
       <c r="C32" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="D32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>104</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
@@ -1641,7 +1703,9 @@
       <c r="C33" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="D33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>106</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
@@ -1653,7 +1717,9 @@
       <c r="C34" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="D34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>108</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
@@ -1665,7 +1731,9 @@
       <c r="C35" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="D35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>110</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
@@ -1677,7 +1745,9 @@
       <c r="C36" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="D36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>112</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
@@ -1689,7 +1759,9 @@
       <c r="C37" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="D37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>114</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
@@ -1701,7 +1773,9 @@
       <c r="C38" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="D38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>116</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
@@ -1713,7 +1787,9 @@
       <c r="C39" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="D39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>118</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
@@ -1725,7 +1801,9 @@
       <c r="C40" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="D40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>120</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
@@ -1737,7 +1815,9 @@
       <c r="C41" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="D41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>122</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
@@ -1749,7 +1829,9 @@
       <c r="C42" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="D42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>124</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
@@ -1761,7 +1843,9 @@
       <c r="C43" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="D43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>126</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
@@ -1773,7 +1857,9 @@
       <c r="C44" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="D44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>128</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
@@ -1785,7 +1871,9 @@
       <c r="C45" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="D45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>130</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
@@ -1797,7 +1885,9 @@
       <c r="C46" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="D46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>132</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
@@ -1809,7 +1899,9 @@
       <c r="C47" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="D47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>134</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
@@ -1821,7 +1913,9 @@
       <c r="C48" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="D48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>136</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
@@ -1833,7 +1927,9 @@
       <c r="C49" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="D49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>138</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
@@ -1845,7 +1941,9 @@
       <c r="C50" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="D50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>140</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
@@ -1857,7 +1955,9 @@
       <c r="C51" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="D51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>142</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
@@ -1869,7 +1969,9 @@
       <c r="C52" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="D52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>144</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
@@ -1881,7 +1983,9 @@
       <c r="C53" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>146</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
@@ -1893,7 +1997,9 @@
       <c r="C54" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="D54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>148</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
@@ -1905,7 +2011,9 @@
       <c r="C55" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="D55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>150</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
@@ -1917,7 +2025,9 @@
       <c r="C56" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="D56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>152</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
@@ -1929,7 +2039,9 @@
       <c r="C57" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="D57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>154</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
@@ -1941,7 +2053,9 @@
       <c r="C58" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="D58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>156</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
@@ -1953,7 +2067,9 @@
       <c r="C59" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="D59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>158</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
@@ -1965,7 +2081,9 @@
       <c r="C60" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="D60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>160</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
@@ -1977,7 +2095,9 @@
       <c r="C61" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="D61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>162</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
@@ -1989,7 +2109,9 @@
       <c r="C62" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="D62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>164</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
@@ -2001,7 +2123,9 @@
       <c r="C63" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="D63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>166</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
@@ -2013,7 +2137,9 @@
       <c r="C64" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="D64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>168</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
@@ -2025,7 +2151,9 @@
       <c r="C65" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="D65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>170</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
@@ -2037,7 +2165,9 @@
       <c r="C66" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="D66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>172</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
@@ -2049,7 +2179,9 @@
       <c r="C67" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="D67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>174</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
@@ -2061,7 +2193,9 @@
       <c r="C68" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="D68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>176</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
@@ -2073,7 +2207,9 @@
       <c r="C69" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="D69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>178</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
@@ -2085,7 +2221,9 @@
       <c r="C70" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="D70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>180</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
@@ -2097,7 +2235,9 @@
       <c r="C71" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="D71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>182</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
@@ -2109,7 +2249,9 @@
       <c r="C72" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="D72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>184</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
@@ -2121,7 +2263,9 @@
       <c r="C73" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="D73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>186</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
@@ -2133,7 +2277,9 @@
       <c r="C74" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="D74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>188</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
@@ -2145,7 +2291,9 @@
       <c r="C75" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="D75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>190</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
@@ -2157,7 +2305,9 @@
       <c r="C76" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="D76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>192</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
@@ -2169,7 +2319,9 @@
       <c r="C77" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="D77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>194</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
@@ -2181,7 +2333,9 @@
       <c r="C78" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="D78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>196</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
@@ -2193,7 +2347,9 @@
       <c r="C79" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="D79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>198</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
@@ -2205,7 +2361,9 @@
       <c r="C80" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="D80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>134</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
@@ -2217,7 +2375,9 @@
       <c r="C81" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="D81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>201</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
@@ -2229,7 +2389,9 @@
       <c r="C82" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="D82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>203</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
@@ -2241,7 +2403,9 @@
       <c r="C83" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="D83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>205</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
@@ -2253,7 +2417,9 @@
       <c r="C84" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="D84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>207</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
@@ -2265,7 +2431,9 @@
       <c r="C85" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="D85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>209</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
@@ -2277,7 +2445,9 @@
       <c r="C86" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="D86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>211</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
@@ -2289,7 +2459,9 @@
       <c r="C87" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="D87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>213</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
@@ -2301,7 +2473,9 @@
       <c r="C88" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="D88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>215</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
@@ -2313,7 +2487,9 @@
       <c r="C89" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="D89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>217</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
@@ -2325,7 +2501,9 @@
       <c r="C90" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="D90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>219</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
@@ -2337,7 +2515,9 @@
       <c r="C91" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="D91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>221</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
@@ -2349,7 +2529,9 @@
       <c r="C92" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="D92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>223</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
@@ -2361,7 +2543,9 @@
       <c r="C93" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="D93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>225</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
@@ -2373,7 +2557,9 @@
       <c r="C94" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="D94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>227</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
@@ -2385,7 +2571,9 @@
       <c r="C95" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="D95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>229</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
@@ -2397,7 +2585,9 @@
       <c r="C96" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="D96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>231</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
@@ -2409,7 +2599,9 @@
       <c r="C97" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="D97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>233</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
@@ -2421,7 +2613,9 @@
       <c r="C98" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="D98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>235</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
@@ -2433,7 +2627,9 @@
       <c r="C99" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="D99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>237</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
@@ -2445,7 +2641,9 @@
       <c r="C100" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="D100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>239</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
@@ -2457,7 +2655,9 @@
       <c r="C101" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="D101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>241</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
@@ -2469,7 +2669,9 @@
       <c r="C102" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="D102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>243</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
@@ -2481,7 +2683,9 @@
       <c r="C103" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="D103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>245</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
@@ -2493,7 +2697,9 @@
       <c r="C104" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="D104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>247</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
@@ -2505,7 +2711,9 @@
       <c r="C105" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="D105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>249</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
@@ -2517,7 +2725,9 @@
       <c r="C106" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="D106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>251</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
@@ -2529,7 +2739,9 @@
       <c r="C107" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="D107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>253</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
@@ -2541,7 +2753,9 @@
       <c r="C108" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="D108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>255</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
@@ -2553,7 +2767,9 @@
       <c r="C109" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="D109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>257</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
@@ -2565,7 +2781,9 @@
       <c r="C110" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="D110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>259</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
@@ -2577,7 +2795,9 @@
       <c r="C111" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="D111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>261</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
@@ -2589,7 +2809,9 @@
       <c r="C112" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="D112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>263</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
@@ -2601,7 +2823,9 @@
       <c r="C113" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="D113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>265</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
@@ -2613,7 +2837,9 @@
       <c r="C114" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="D114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>267</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
@@ -2625,7 +2851,9 @@
       <c r="C115" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="D115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>269</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
@@ -2637,7 +2865,9 @@
       <c r="C116" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="D116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>271</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
@@ -2649,7 +2879,9 @@
       <c r="C117" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="D117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>273</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
@@ -2661,7 +2893,9 @@
       <c r="C118" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="D118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>275</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
@@ -2673,7 +2907,9 @@
       <c r="C119" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="D119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>277</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
@@ -2685,7 +2921,9 @@
       <c r="C120" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="D120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>279</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
@@ -2697,7 +2935,9 @@
       <c r="C121" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="D121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>281</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
@@ -2709,7 +2949,9 @@
       <c r="C122" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="D122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>283</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
@@ -2721,7 +2963,9 @@
       <c r="C123" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="D123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>285</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
@@ -2733,7 +2977,9 @@
       <c r="C124" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="D124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>287</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
@@ -2745,7 +2991,9 @@
       <c r="C125" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="D125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>289</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
@@ -2757,7 +3005,9 @@
       <c r="C126" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="D126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>291</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
@@ -2769,7 +3019,9 @@
       <c r="C127" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="D127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>293</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
@@ -2781,7 +3033,9 @@
       <c r="C128" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="D128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>295</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
@@ -2793,7 +3047,9 @@
       <c r="C129" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="D129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>297</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
@@ -2805,7 +3061,9 @@
       <c r="C130" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="D130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>299</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
@@ -2817,7 +3075,9 @@
       <c r="C131" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="D131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>301</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
@@ -2829,7 +3089,9 @@
       <c r="C132" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="D132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>303</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -585,7 +585,7 @@
     <t>552</t>
   </si>
   <si>
-    <t xml:space="preserve">Entraînement à l'hémodialyse </t>
+    <t>Entraînement à l'hémodialyse</t>
   </si>
   <si>
     <t>553</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-discipline-equipement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
